--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92556427931</v>
+        <v>46157.93116841973</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93116841973</v>
+        <v>46157.9313940014</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9313940014</v>
+        <v>46157.93386196083</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93386196083</v>
+        <v>46157.93697886232</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93697886232</v>
+        <v>46158.2820601807</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2820601807</v>
+        <v>46158.29654874008</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29654874008</v>
+        <v>46158.29809987663</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29809987663</v>
+        <v>46158.33372312552</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33372312552</v>
+        <v>46158.37224323409</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37224323409</v>
+        <v>46158.37276607095</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
